--- a/diseases/d237/2020-2025.xlsx
+++ b/diseases/d237/2020-2025.xlsx
@@ -10297,13 +10297,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="O50" t="n">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="R50" t="n">
-        <v>7.373178804434256</v>
+        <v>7.363578311199316</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -10456,10 +10456,10 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="O51" t="n">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
@@ -13451,13 +13451,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="O66" t="n">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R66" t="n">
-        <v>6.93216905948869</v>
+        <v>6.92263375129132</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13610,10 +13610,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="O67" t="n">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -24475,13 +24475,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="O122" t="n">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="R122" t="n">
-        <v>9.936835102935335</v>
+        <v>9.927407365646022</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -24634,10 +24634,10 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="O123" t="n">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>65361</v>
+        <v>65358</v>
       </c>
     </row>
     <row r="16">
